--- a/scripts/Revenue forecast error math for US.xlsx
+++ b/scripts/Revenue forecast error math for US.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xabajian/Documents/GitHub/ACF_NK_Measurement/scripts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5234BD23-63B7-994C-92F4-8858CDBAF939}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEF87830-23A7-9A43-A72D-0215B76332C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{8595BB93-C4CF-CF41-8EE4-01E47DE92020}"/>
   </bookViews>
@@ -565,7 +565,7 @@
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="28.1640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.33203125" customWidth="1"/>
-    <col min="6" max="6" width="20.33203125" customWidth="1"/>
+    <col min="6" max="6" width="25.33203125" customWidth="1"/>
     <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.83203125" bestFit="1" customWidth="1"/>
@@ -637,15 +637,15 @@
         <v>31.5</v>
       </c>
       <c r="D4" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E4" s="2">
         <f>B4+D4</f>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F4" s="2">
         <f>F3*E4</f>
-        <v>31.521890432999999</v>
+        <v>31.534943999999999</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
@@ -664,15 +664,15 @@
         <v>33.075000000000003</v>
       </c>
       <c r="D5" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" ref="E5:E13" si="3">B5+D5</f>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" ref="F5:F13" si="4">F4*E5</f>
-        <v>33.120985882335226</v>
+        <v>33.148423102771197</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="2"/>
@@ -691,15 +691,15 @@
         <v>34.728750000000005</v>
       </c>
       <c r="D6" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="4"/>
-        <v>34.801202933863692</v>
+        <v>34.844455541139865</v>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
@@ -718,15 +718,15 @@
         <v>36.465187500000006</v>
       </c>
       <c r="D7" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E7" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="4"/>
-        <v>36.566656860594982</v>
+        <v>36.627265140011176</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="2"/>
@@ -745,15 +745,15 @@
         <v>38.288446875000005</v>
       </c>
       <c r="D8" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E8" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="4"/>
-        <v>38.421671702026089</v>
+        <v>38.501291835446821</v>
       </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
@@ -772,15 +772,15 @@
         <v>40.20286921875001</v>
       </c>
       <c r="D9" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E9" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="4"/>
-        <v>40.370790854798763</v>
+        <v>40.471202731949091</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
@@ -799,15 +799,15 @@
         <v>42.213012679687509</v>
       </c>
       <c r="D10" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E10" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="4"/>
-        <v>42.418788200617499</v>
+        <v>42.541903725488723</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -826,15 +826,15 @@
         <v>44.323663313671886</v>
       </c>
       <c r="D11" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E11" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="4"/>
-        <v>44.570679798683265</v>
+        <v>44.71855172122261</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
@@ -853,15 +853,15 @@
         <v>46.539846479355482</v>
       </c>
       <c r="D12" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E12" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="4"/>
-        <v>46.831736171280681</v>
+        <v>47.00656747632862</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
@@ -882,15 +882,15 @@
         <v>48.866838803323262</v>
       </c>
       <c r="D13" s="4">
-        <v>7.2968109999999996E-4</v>
+        <v>1.1647999999999999E-3</v>
       </c>
       <c r="E13" s="2">
         <f t="shared" si="3"/>
-        <v>1.0507296811</v>
+        <v>1.0511648</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="4"/>
-        <v>49.207495212609082</v>
+        <v>49.411649099941478</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -914,15 +914,15 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2">
         <f>SUM(F4:F13)</f>
-        <v>397.8318980498093</v>
+        <v>398.80625437429956</v>
       </c>
       <c r="G14" s="2">
         <f>C14-F14</f>
-        <v>-1.6282831800210715</v>
+        <v>-2.6026395045113304</v>
       </c>
       <c r="H14" s="2">
         <f>G14*0.2</f>
-        <v>-0.32565663600421435</v>
+        <v>-0.52052790090226608</v>
       </c>
       <c r="I14" s="5">
         <v>0.52300000000000002</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="M16">
         <f>H14/M15</f>
-        <v>-0.28496298519730223</v>
+        <v>-0.45548337764465419</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -964,7 +964,7 @@
       </c>
       <c r="M17">
         <f>H14/G14</f>
-        <v>0.20000000000000004</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="18" spans="1:13">
